--- a/data/xlsx/isc-t-h--food-and-beverage-service.xlsx
+++ b/data/xlsx/isc-t-h--food-and-beverage-service.xlsx
@@ -647,7 +647,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -669,7 +671,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -691,7 +695,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -713,7 +719,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -735,7 +743,9 @@
       <c r="C20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -757,7 +767,9 @@
       <c r="C21" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -779,7 +791,9 @@
       <c r="C22" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -805,7 +819,9 @@
       <c r="C23" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -831,7 +847,9 @@
       <c r="C24" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -857,7 +875,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -879,7 +899,9 @@
       <c r="C26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -901,7 +923,9 @@
       <c r="C27" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -923,7 +947,9 @@
       <c r="C28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -945,7 +971,9 @@
       <c r="C29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -967,7 +995,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -989,7 +1019,9 @@
       <c r="C31" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -1011,7 +1043,9 @@
       <c r="C32" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
@@ -1033,7 +1067,9 @@
       <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -1055,7 +1091,9 @@
       <c r="C34" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -1077,7 +1115,9 @@
       <c r="C35" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1099,7 +1139,9 @@
       <c r="C36" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -1121,7 +1163,9 @@
       <c r="C37" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>4</v>
       </c>
@@ -1143,7 +1187,9 @@
       <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
@@ -1165,7 +1211,9 @@
       <c r="C39" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
@@ -1187,7 +1235,9 @@
       <c r="C40" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>4</v>
       </c>
@@ -1209,7 +1259,9 @@
       <c r="C41" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
@@ -1235,7 +1287,9 @@
       <c r="C42" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>3</v>
       </c>
@@ -1257,7 +1311,9 @@
       <c r="C43" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>3</v>
       </c>
@@ -1279,7 +1335,9 @@
       <c r="C44" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>3</v>
       </c>
@@ -1301,7 +1359,9 @@
       <c r="C45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="9" t="n">
         <v>3</v>
       </c>
@@ -1323,7 +1383,9 @@
       <c r="C46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="9" t="n"/>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="9" t="n">
         <v>3</v>
       </c>

--- a/data/xlsx/isc-t-h--food-and-beverage-service.xlsx
+++ b/data/xlsx/isc-t-h--food-and-beverage-service.xlsx
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -903,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" s="9">
         <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37" s="9">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
@@ -1191,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" s="9">
         <f>IFERROR(MIN(C38,D38)*E38/C38,0)</f>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" s="9">
         <f>IFERROR(MIN(C39,D39)*E39/C39,0)</f>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" s="9">
         <f>IFERROR(MIN(C40,D40)*E40/C40,0)</f>
